--- a/Tables/Pretreat_pairwise_adonis_same_sheet.xlsx
+++ b/Tables/Pretreat_pairwise_adonis_same_sheet.xlsx
@@ -17,10 +17,10 @@
     <t xml:space="preserve">parent_call</t>
   </si>
   <si>
-    <t xml:space="preserve">Veg_Spp ~ Treatment , strata = Null , permutations 999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soil Inversion_vs_Preemergent</t>
+    <t xml:space="preserve">Spp ~ Treatment , strata = Null , permutations 999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control_vs_Fill</t>
   </si>
   <si>
     <t xml:space="preserve">Df</t>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">Pr(&gt;F)</t>
   </si>
   <si>
-    <t xml:space="preserve">Soil Inversion_vs_Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soil Inversion_vs_Fill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preemergent_vs_Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preemergent_vs_Fill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control_vs_Fill</t>
+    <t xml:space="preserve">Control_vs_Preemergent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control_vs_Soil Inversion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill_vs_Preemergent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill_vs_Soil Inversion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preemergent_vs_Soil Inversion</t>
   </si>
 </sst>
 </file>
@@ -416,37 +416,37 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00520033280587158</v>
+        <v>0.000567806982102463</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0132524658015367</v>
+        <v>0.0492395693976069</v>
       </c>
       <c r="D6" t="n">
-        <v>1.58479338471477</v>
+        <v>0.517896704708348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.127</v>
+        <v>0.8707</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>0.387204588946015</v>
+        <v>0.0109637110439276</v>
       </c>
       <c r="C7" t="n">
-        <v>0.986747534198463</v>
+        <v>0.950760430602393</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>0.392404921751887</v>
+        <v>0.0115315180260301</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -481,37 +481,37 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00595919875172823</v>
+        <v>0.000389764132980701</v>
       </c>
       <c r="C12" t="n">
-        <v>0.013417002286724</v>
+        <v>0.0336504347188096</v>
       </c>
       <c r="D12" t="n">
-        <v>1.60473703023773</v>
+        <v>0.348222174747064</v>
       </c>
       <c r="E12" t="n">
-        <v>0.173</v>
+        <v>0.9412</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>0.438193572812214</v>
+        <v>0.0111929727985821</v>
       </c>
       <c r="C13" t="n">
-        <v>0.986582997713276</v>
+        <v>0.96634956528119</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>0.444152771563942</v>
+        <v>0.0115827369315628</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -546,37 +546,37 @@
         <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.00862772024146732</v>
+        <v>0.000994710795829166</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0206239110456925</v>
+        <v>0.0581900480589019</v>
       </c>
       <c r="D18" t="n">
-        <v>2.48486922525352</v>
+        <v>0.617853399605414</v>
       </c>
       <c r="E18" t="n">
-        <v>0.013</v>
+        <v>0.7445</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="B19" t="n">
-        <v>0.40970807563898</v>
+        <v>0.0160994630192927</v>
       </c>
       <c r="C19" t="n">
-        <v>0.979376088954308</v>
+        <v>0.941809951941098</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="B20" t="n">
-        <v>0.418335795880447</v>
+        <v>0.0170941738151219</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -611,37 +611,37 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00337709779867463</v>
+        <v>0.000236674736411677</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0091989045152944</v>
+        <v>0.0237618422053353</v>
       </c>
       <c r="D24" t="n">
-        <v>1.09554857958016</v>
+        <v>0.243402104451782</v>
       </c>
       <c r="E24" t="n">
-        <v>0.372</v>
+        <v>0.9752</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="B25" t="n">
-        <v>0.363742464433954</v>
+        <v>0.00972361093363356</v>
       </c>
       <c r="C25" t="n">
-        <v>0.990801095484706</v>
+        <v>0.976238157794665</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="B26" t="n">
-        <v>0.367119562232629</v>
+        <v>0.00996028567004524</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -676,37 +676,37 @@
         <v>1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.00494654672754384</v>
+        <v>0.00175040208590974</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0145399636516232</v>
+        <v>0.106858871198063</v>
       </c>
       <c r="D30" t="n">
-        <v>1.74103022711009</v>
+        <v>1.1964388129948</v>
       </c>
       <c r="E30" t="n">
-        <v>0.121</v>
+        <v>0.3173</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="B31" t="n">
-        <v>0.33525696726072</v>
+        <v>0.0146301011543442</v>
       </c>
       <c r="C31" t="n">
-        <v>0.985460036348377</v>
+        <v>0.893141128801937</v>
       </c>
       <c r="D31"/>
       <c r="E31"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="B32" t="n">
-        <v>0.340203513988264</v>
+        <v>0.0163805032402539</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -741,37 +741,37 @@
         <v>1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.00378681448088016</v>
+        <v>0.00105969136032755</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00970896502753828</v>
+        <v>0.066567482112893</v>
       </c>
       <c r="D36" t="n">
-        <v>1.15689007856299</v>
+        <v>0.713147237076906</v>
       </c>
       <c r="E36" t="n">
-        <v>0.321</v>
+        <v>0.6541</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="B37" t="n">
-        <v>0.386245951126919</v>
+        <v>0.0148593629089987</v>
       </c>
       <c r="C37" t="n">
-        <v>0.990291034972462</v>
+        <v>0.933432517887107</v>
       </c>
       <c r="D37"/>
       <c r="E37"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="B38" t="n">
-        <v>0.390032765607799</v>
+        <v>0.0159190542693262</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
